--- a/SGC-CKN/Excel/cdab2cae-a0c4-46ae-a173-e6f833b4aece_Thanh_Hoá_P7-43_D800_07-04-2026.xlsx
+++ b/SGC-CKN/Excel/cdab2cae-a0c4-46ae-a173-e6f833b4aece_Thanh_Hoá_P7-43_D800_07-04-2026.xlsx
@@ -1262,7 +1262,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
         <v>-7.06</v>
@@ -1271,10 +1271,10 @@
         <v>0.22</v>
       </c>
       <c r="I11" s="5">
-        <v>6.46</v>
+        <v>7.06</v>
       </c>
       <c r="J11" s="8">
-        <v>29.82</v>
+        <v>32.58</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1300,16 +1300,16 @@
         <v>-7.06</v>
       </c>
       <c r="G12" s="9">
-        <v>-9.05</v>
+        <v>-9.06</v>
       </c>
       <c r="H12" s="9">
         <v>0.05</v>
       </c>
       <c r="I12" s="9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J12" s="8">
-        <v>39.8</v>
+        <v>40</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
@@ -1332,7 +1332,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="12">
-        <v>-9.05</v>
+        <v>-9.06</v>
       </c>
       <c r="G13" s="12">
         <v>-17.06</v>
@@ -1341,10 +1341,10 @@
         <v>1.28</v>
       </c>
       <c r="I13" s="12">
-        <v>8.01</v>
+        <v>8</v>
       </c>
       <c r="J13" s="8">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>39</v>
@@ -1440,16 +1440,16 @@
         <v>-26.56</v>
       </c>
       <c r="G16" s="21">
-        <v>-36.56</v>
+        <v>-36.29</v>
       </c>
       <c r="H16" s="21">
         <v>1.87</v>
       </c>
       <c r="I16" s="21">
-        <v>10</v>
+        <v>9.73</v>
       </c>
       <c r="J16" s="8">
-        <v>5.36</v>
+        <v>5.21</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
@@ -1472,19 +1472,19 @@
         <v>56</v>
       </c>
       <c r="F17" s="24">
-        <v>-36.56</v>
+        <v>-36.29</v>
       </c>
       <c r="G17" s="24">
-        <v>-38.5</v>
+        <v>-38.29</v>
       </c>
       <c r="H17" s="24">
         <v>0.42</v>
       </c>
       <c r="I17" s="24">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="J17" s="27">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>30</v>
@@ -1507,7 +1507,7 @@
         <v>60</v>
       </c>
       <c r="F18" s="28">
-        <v>-38.5</v>
+        <v>-38.29</v>
       </c>
       <c r="G18" s="28">
         <v>-39.5</v>
@@ -1516,10 +1516,10 @@
         <v>3.73</v>
       </c>
       <c r="I18" s="28">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="J18" s="31">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>61</v>
@@ -1744,7 +1744,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
         <v>-7.06</v>
@@ -1753,10 +1753,10 @@
         <v>0.22</v>
       </c>
       <c r="H2" s="5">
-        <v>6.46</v>
+        <v>7.06</v>
       </c>
       <c r="I2" s="8">
-        <v>29.82</v>
+        <v>32.58</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1776,16 +1776,16 @@
         <v>-7.06</v>
       </c>
       <c r="F3" s="9">
-        <v>-9.05</v>
+        <v>-9.06</v>
       </c>
       <c r="G3" s="9">
         <v>0.05</v>
       </c>
       <c r="H3" s="9">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I3" s="8">
-        <v>39.8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1802,7 +1802,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="12">
-        <v>-9.05</v>
+        <v>-9.06</v>
       </c>
       <c r="F4" s="12">
         <v>-17.06</v>
@@ -1811,10 +1811,10 @@
         <v>1.28</v>
       </c>
       <c r="H4" s="12">
-        <v>8.01</v>
+        <v>8</v>
       </c>
       <c r="I4" s="8">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1892,16 +1892,16 @@
         <v>-26.56</v>
       </c>
       <c r="F7" s="21">
-        <v>-36.56</v>
+        <v>-36.29</v>
       </c>
       <c r="G7" s="21">
         <v>1.87</v>
       </c>
       <c r="H7" s="21">
-        <v>10</v>
+        <v>9.73</v>
       </c>
       <c r="I7" s="8">
-        <v>5.36</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1918,19 +1918,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="24">
-        <v>-36.56</v>
+        <v>-36.29</v>
       </c>
       <c r="F8" s="24">
-        <v>-38.5</v>
+        <v>-38.29</v>
       </c>
       <c r="G8" s="24">
         <v>0.42</v>
       </c>
       <c r="H8" s="24">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="I8" s="27">
-        <v>4.66</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1947,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-38.5</v>
+        <v>-38.29</v>
       </c>
       <c r="F9" s="28">
         <v>-39.5</v>
@@ -1956,10 +1956,10 @@
         <v>3.73</v>
       </c>
       <c r="H9" s="28">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="I9" s="31">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2034,7 +2034,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="40">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="F12" s="40">
         <v>-44.9</v>
@@ -2043,10 +2043,10 @@
         <v>10.37</v>
       </c>
       <c r="H12" s="40">
-        <v>44.3</v>
+        <v>44.9</v>
       </c>
       <c r="I12" s="40">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
     </row>
   </sheetData>
